--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-01-2026.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.77</t>
+          <t>£10.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.77</t>
+          <t>£10.55</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.77</t>
+          <t>£10.55</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£10.55</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£12.20</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>£15.41</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>£16.01</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£20.17</t>
+          <t>£19.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£20.17</t>
+          <t>£19.76</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£20.17</t>
+          <t>£19.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£19.96</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£22.33</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£22.37</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.37</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£22.37</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£22.16</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.94</t>
+          <t>£25.04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.94</t>
+          <t>£25.04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.94</t>
+          <t>£25.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>£25.63</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£28.22</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.22</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£28.22</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£27.74</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£27.74</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£27.74</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>£27.49</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1453,17 +1453,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£35.72</t>
+          <t>£35.30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£35.72</t>
+          <t>£35.30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£35.72</t>
+          <t>£35.30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>£35.19</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>£31.98</t>
+          <t>£32.14</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>£33.50</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>£41.14</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£42.11</t>
+          <t>£42.85</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£42.11</t>
+          <t>£42.85</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>£42.35</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>£41.25</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1891,7 +1891,36 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>£39.12</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.629
+  (Session info: chrome=144.0.7559.98)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff7226ea535
+	0x7ff7226ea590
+	0x7ff7224910bd
+	0x7ff72247dda9
+	0x7ff72247da91
+	0x7ff72247b6a7
+	0x7ff72247bfff
+	0x7ff72248b45a
+	0x7ff7224a2387
+	0x7ff7224a9a8a
+	0x7ff72247c7c1
+	0x7ff7224a20b4
+	0x7ff72253a26f
+	0x7ff7224dcc9c
+	0x7ff7224ddbe3
+	0x7ff7229c7b60
+	0x7ff7229c1f5d
+	0x7ff7229e311a
+	0x7ff7227060a5
+	0x7ff72270e73c
+	0x7ff7226f3844
+	0x7ff7226f39f6
+	0x7ff7226d9a07
+	0x7ffc5df1e8d7
+	0x7ffc5f24c53c
+</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1913,17 +1942,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£766.67</t>
+          <t>£765.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£766.67</t>
+          <t>£765.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£766.67</t>
+          <t>£765.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1973,7 +2002,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>£791.88</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2005,17 +2034,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£988.89</t>
+          <t>£985.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£985.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£988.89</t>
+          <t>£985.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2065,7 +2094,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>£1029.48</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2097,17 +2126,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£29.88</t>
+          <t>£29.30</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£29.88</t>
+          <t>£29.30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£29.88</t>
+          <t>£29.30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2157,7 +2186,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£29.26</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2189,17 +2218,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£35.14</t>
+          <t>£35.54</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£35.14</t>
+          <t>£35.54</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£35.14</t>
+          <t>£35.54</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2249,7 +2278,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£35.59</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2281,17 +2310,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£39.52</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£39.52</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£39.52</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2341,7 +2370,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£39.10</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2373,17 +2402,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£44.94</t>
+          <t>£42.55</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£44.94</t>
+          <t>£42.55</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£44.94</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2433,7 +2462,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£44.44</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2465,17 +2494,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£48.22</t>
+          <t>£47.45</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£47.45</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£48.22</t>
+          <t>£47.45</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2525,7 +2554,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>£48.17</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2535,7 +2564,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>£44.81</t>
+          <t>£42.57</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2557,17 +2586,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£48.33</t>
+          <t>£45.40</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>£48.33</t>
+          <t>£45.40</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£48.33</t>
+          <t>£45.40</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2617,7 +2646,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>£47.58</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2649,17 +2678,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>£1,027.78</t>
+          <t>£925.79</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>£1,027.78</t>
+          <t>£925.79</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£1,027.78</t>
+          <t>£925.79</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2709,7 +2738,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>£1,016.40</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2741,17 +2770,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£47.44</t>
+          <t>£42.95</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£47.44</t>
+          <t>£42.95</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£47.44</t>
+          <t>£42.95</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2786,7 +2815,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2801,7 +2830,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>£47.08</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2833,17 +2862,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£1,233.33</t>
+          <t>£1,202.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>£1,233.33</t>
+          <t>£1,202.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,233.33</t>
+          <t>£1,202.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2893,7 +2922,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>£1267.2</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2925,17 +2954,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£1,353.33</t>
+          <t>£1,319.33</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>£1,353.33</t>
+          <t>£1,319.33</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>£1,353.33</t>
+          <t>£1,319.33</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2985,7 +3014,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>£1408.0</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3017,17 +3046,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£1,355.56</t>
+          <t>£1,275.65</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>£1,355.56</t>
+          <t>£1,275.65</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,355.56</t>
+          <t>£1,275.65</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3077,7 +3106,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>£1408.0</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
